--- a/Team-Data/2012-13/3-25-2012-13.xlsx
+++ b/Team-Data/2012-13/3-25-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.549</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,7 +746,7 @@
         <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.465</v>
@@ -688,31 +755,31 @@
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
         <v>13.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V2" t="n">
         <v>15.1</v>
@@ -724,34 +791,34 @@
         <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
         <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB2" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -796,16 +863,16 @@
         <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -945,7 +1012,7 @@
         <v>9</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>27</v>
@@ -972,10 +1039,10 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>11</v>
@@ -1163,7 +1230,7 @@
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1357,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1476,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1488,7 +1555,7 @@
         <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1670,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>-0.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF8" t="n">
         <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.681</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L9" t="n">
         <v>6.4</v>
@@ -1965,28 +2032,28 @@
         <v>18.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.698</v>
+        <v>0.696</v>
       </c>
       <c r="R9" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="S9" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U9" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V9" t="n">
         <v>15.3</v>
@@ -2001,16 +2068,16 @@
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -2019,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
@@ -2034,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
@@ -2052,13 +2119,13 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2088,7 +2155,7 @@
         <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2262,10 @@
         <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>26</v>
@@ -2213,10 +2280,10 @@
         <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2234,7 +2301,7 @@
         <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.455</v>
@@ -2338,19 +2405,19 @@
         <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.791</v>
+        <v>0.792</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T11" t="n">
         <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
@@ -2365,22 +2432,22 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>10</v>
@@ -2389,10 +2456,10 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2416,7 +2483,7 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2437,22 +2504,22 @@
         <v>28</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2571,7 +2638,7 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2622,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
         <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>0.614</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
         <v>0.356</v>
@@ -2699,7 +2766,7 @@
         <v>17.2</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
         <v>0.75</v>
@@ -2714,10 +2781,10 @@
         <v>46.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2735,13 +2802,13 @@
         <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2762,7 +2829,7 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
@@ -2771,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2807,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2816,7 +2883,7 @@
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2932,7 +2999,7 @@
         <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -2941,16 +3008,16 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>21</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
         <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,40 +3112,40 @@
         <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M15" t="n">
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S15" t="n">
         <v>33.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3102,10 +3169,10 @@
         <v>102.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3123,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3156,10 +3223,10 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>24</v>
@@ -3171,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="n">
         <v>47</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,7 +3294,7 @@
         <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.443</v>
@@ -3248,13 +3315,13 @@
         <v>20.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
         <v>42.8</v>
@@ -3272,40 +3339,40 @@
         <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB16" t="n">
         <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
@@ -3347,13 +3414,13 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3415,13 +3482,13 @@
         <v>0.496</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O17" t="n">
         <v>17.7</v>
@@ -3430,7 +3497,7 @@
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R17" t="n">
         <v>8.300000000000001</v>
@@ -3442,10 +3509,10 @@
         <v>38.5</v>
       </c>
       <c r="U17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V17" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W17" t="n">
         <v>8.9</v>
@@ -3454,22 +3521,22 @@
         <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z17" t="n">
         <v>18.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3493,10 +3560,10 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3672,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
@@ -3851,10 +3918,10 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3884,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -3937,37 +4004,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.352</v>
+        <v>0.343</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J20" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.368</v>
+        <v>0.364</v>
       </c>
       <c r="O20" t="n">
         <v>14.9</v>
@@ -3976,25 +4043,25 @@
         <v>19.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>29.7</v>
       </c>
       <c r="T20" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>14.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X20" t="n">
         <v>5.6</v>
@@ -4003,28 +4070,28 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA20" t="n">
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,10 +4100,10 @@
         <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4045,13 +4112,13 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4273,7 @@
         <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>29</v>
@@ -4266,7 +4333,7 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.254</v>
+        <v>0.257</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4510,10 +4577,10 @@
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O23" t="n">
         <v>12.3</v>
@@ -4522,7 +4589,7 @@
         <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
@@ -4546,7 +4613,7 @@
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
         <v>19.5</v>
@@ -4558,10 +4625,10 @@
         <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,19 +4640,19 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
         <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>16</v>
@@ -4600,28 +4667,28 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -4665,58 +4732,58 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" t="n">
         <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>0.386</v>
+        <v>0.391</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R24" t="n">
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="V24" t="n">
         <v>13.2</v>
@@ -4728,22 +4795,22 @@
         <v>4.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>18.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
         <v>92.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4964,7 +5031,7 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR25" t="n">
         <v>11</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5137,13 +5204,13 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ26" t="n">
         <v>7</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,19 +5550,19 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5510,7 +5577,7 @@
         <v>18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5668,10 +5735,10 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
@@ -5716,7 +5783,7 @@
         <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O30" t="n">
         <v>18.3</v>
@@ -5796,7 +5863,7 @@
         <v>23.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R30" t="n">
         <v>12.4</v>
@@ -5805,7 +5872,7 @@
         <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U30" t="n">
         <v>22.4</v>
@@ -5817,7 +5884,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y30" t="n">
         <v>6</v>
@@ -5826,16 +5893,16 @@
         <v>21.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5844,10 +5911,10 @@
         <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
@@ -5859,7 +5926,7 @@
         <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
         <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
@@ -5957,28 +6024,28 @@
         <v>35.6</v>
       </c>
       <c r="J31" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L31" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M31" t="n">
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O31" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="P31" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.735</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
         <v>10.7</v>
@@ -5990,10 +6057,10 @@
         <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6002,31 +6069,31 @@
         <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF31" t="n">
         <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH31" t="n">
         <v>8</v>
@@ -6035,10 +6102,10 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6047,16 +6114,16 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>23</v>
@@ -6068,13 +6135,13 @@
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV31" t="n">
         <v>27</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -6086,10 +6153,10 @@
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-25-2012-13</t>
+          <t>2013-03-25</t>
         </is>
       </c>
     </row>
